--- a/important_mails_2026-04-08.xlsx
+++ b/important_mails_2026-04-08.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -543,12 +543,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -558,21 +558,223 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
+          <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
+          <t>EU and UK Compliance Brief</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe
+ 96
+ EU and UK Compliance Brief
+ To better support your compliance journey, we've prepared an overview of regulations that affect your business in Amazon’s European stores. For more information on all compliance requirements, go to
+ European compliance requirements
+ Country of Origin (COO), EU &amp; UK
+ Am I impacted?
+ Yes, if you ship across borders to customers:
+ - From outside the EU into the EU through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
+ - From outside the UK into the UK through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
+ Consequences of not meeting the requirement:
+ To avoid disruptions to your business, provide this information to your listings by June 30, 2026.
+ How do I become compliant?
+ You can use the Category Listings Report (CLR) to update the COO information for your existing product listings in bulk:
+- Download the CLR from the “Inventory Reports” page on Seller Central
+- Edit the Country of Origin column for all your produ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>EU and UK Compliance Brief</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe
+ 96
+ EU and UK Compliance Brief
+ To better support your compliance journey, we've prepared an overview of regulations that affect your business in Amazon’s European stores. For more information on all compliance requirements, go to
+ European compliance requirements
+ Country of Origin (COO), EU &amp; UK
+ Am I impacted?
+ Yes, if you ship across borders to customers:
+ - From outside the EU into the EU through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
+ - From outside the UK into the UK through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
+ Consequences of not meeting the requirement:
+ To avoid disruptions to your business, provide this information to your listings by June 30, 2026.
+ How do I become compliant?
+ You can use the Category Listings Report (CLR) to update the COO information for your existing product listings in bulk:
+- Download the CLR from the “Inventory Reports” page on Seller Central
+- Edit the Country of Origin column for all your produ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>VAT Calculation Services will calculate VAT by shipment as of June
+ 1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+ New tax calculation method ensures compliance with European e-invoicing mandates.
+ Hello,
+ Effective as of June 1, 2026, we’re updating Value Added Tax (VAT) Calculation Services (VCS) to comply with European e-invoicing mandates. Instead of calculating VAT per unit, VCS will calculate VAT on the total invoice amount by tax rate. This means when customers buy multiple units, the total invoice amounts may differ from current calculations.
+ Depending on the sales channel (regardless of customer VAT registration), VCS will apply one of two methods:
+- Consumer website : VCS will impute VAT from the VAT-inclusive price. If multiple units are purchased, unit exclusive prices may vary.
+- Amazon Business website : VCS will derive the VAT-exclusive unit price from the VAT-inclusive unit price. VAT will be calculated on the total VAT-exclusive price by tax rate. For more information about invoice-total VAT calculations and to view examples, go to section 10: Invoice-total VAT calculation method of VAT Calculation Services methodology .
+ The Amazon Europe team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notific</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Votre paiement est en cours</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
+Le 04/08/26 15:00 CEST, nous avons effectué un virement d’un montant de €
+ 26.11 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pé</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -593,39 +795,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -651,39 +853,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -697,40 +899,40 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -747,39 +949,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -799,39 +1001,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -848,39 +1050,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -903,39 +1105,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -953,39 +1155,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1003,39 +1205,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1047,39 +1249,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1091,39 +1293,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1135,39 +1337,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1179,39 +1381,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1223,39 +1425,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1267,39 +1469,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1311,39 +1513,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1355,39 +1557,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1399,39 +1601,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1450,39 +1652,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1494,39 +1696,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1538,39 +1740,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1582,39 +1784,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1626,39 +1828,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1670,39 +1872,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1714,39 +1916,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1758,39 +1960,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1809,39 +2011,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1853,40 +2055,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1905,39 +2107,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1949,39 +2151,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2000,39 +2202,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -2064,39 +2266,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -2123,39 +2325,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -2167,39 +2369,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -2209,39 +2411,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -2251,39 +2453,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -2296,39 +2498,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -2337,39 +2539,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2387,39 +2589,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2439,40 +2641,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2488,39 +2690,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2540,39 +2742,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2598,39 +2800,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2646,39 +2848,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2699,39 +2901,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2745,40 +2947,40 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -2794,39 +2996,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2846,39 +3048,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2892,39 +3094,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2944,39 +3146,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2999,39 +3201,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3051,39 +3253,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3100,39 +3302,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3149,39 +3351,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -3196,39 +3398,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3252,39 +3454,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3298,39 +3500,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3350,39 +3552,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3400,39 +3602,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3450,39 +3652,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3500,39 +3702,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3547,39 +3749,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3597,39 +3799,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3647,39 +3849,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3697,39 +3899,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3744,39 +3946,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3791,39 +3993,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3838,39 +4040,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3889,40 +4091,40 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3941,39 +4143,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3983,39 +4185,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4033,39 +4235,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4081,39 +4283,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4132,39 +4334,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4182,39 +4384,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -4236,39 +4438,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -4291,39 +4493,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -4353,39 +4555,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -4403,39 +4605,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4452,39 +4654,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4500,39 +4702,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -4561,39 +4763,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -4614,39 +4816,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4661,39 +4863,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -4707,40 +4909,40 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -4756,39 +4958,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4804,39 +5006,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -4852,39 +5054,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4900,40 +5102,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4949,39 +5151,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4999,39 +5201,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -5047,39 +5249,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5094,39 +5296,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -5141,39 +5343,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5194,40 +5396,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -5242,39 +5444,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -5295,39 +5497,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -5360,39 +5562,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5408,39 +5610,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5456,39 +5658,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5506,39 +5708,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5555,39 +5757,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -5611,39 +5813,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5658,39 +5860,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -5706,39 +5908,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5755,40 +5957,40 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -5804,39 +6006,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -5856,39 +6058,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -5904,40 +6106,40 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5953,39 +6155,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6002,140 +6204,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.ca
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 2/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>Hola Weihai EU,
-Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
-Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
-¿Estaría disponible para una reunión online esta semana?
-Acerca de Worten - Somos el líder del mercado portugués:
-- Nº 1 del comercio electrónico portugués
-- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
-- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
-- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
-- Sin costes iniciales - 6 meses
-Estaré encantado de ayudarle si tiene alguna pregunta.
-Muchas gracias,
-Saludos Cordiales</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6156,39 +6257,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6211,39 +6312,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6264,39 +6365,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6320,39 +6421,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6375,39 +6476,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6430,39 +6531,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6484,39 +6585,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6546,39 +6647,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6594,39 +6695,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6642,40 +6743,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6694,40 +6795,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6745,39 +6846,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -6791,39 +6892,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
